--- a/public/inputs/y10-portuguese-1st - input.xlsx
+++ b/public/inputs/y10-portuguese-1st - input.xlsx
@@ -8,8 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source export" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contents'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source export'!$A$1:$B$69</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +29,76 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00243746"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00173047"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="00243746"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00187A78"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00243746"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="00243746"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00173047"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F3F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -42,12 +106,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00187A78"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="hair">
+        <color rgb="00D4DEE3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -410,277 +514,954 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00187A78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Section type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Unit 1 · Reading: Comprehension of texts</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 0 - Avaliação Diagnóstica</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 1 - Paper 1, Question 1: Ficção do Século XXI</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 2 - Ficção e Não Ficção dos Séculos XX e XXI</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Subunit</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Texts: Narrative, Descriptive, Discursive, Argumentative, Letter, Summary, Report, Email, Speech - 1st Term</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.1 - Paper 1, Question 2: Imagem e Estrutura</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Subunit</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Texts: Narrative, Descriptive, Discursive, Argumentative, Letter, Summary, Report, Email, Speech - 2nd Term</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.2 - Paper 1, Question 2: Voz, Ironia e Enviesamento</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Subunit</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Texts: Narrative, Descriptive, Discursive, Argumentative, Letter, Summary, Report, Email, Speech - 3rd Term</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.3 - Texto Narrativo - Maria Judite de Carvalho - As Palavras Poupadas</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.4 - Literaturas de Língua Portuguesa dos Séculos XX e XXI</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.5 - Texto Narrativo - José Saramago - A Viagem do Elefante</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.6 - Texto Narrativo - Mia Couto - O Embondeiro que Sonhava Pássaros</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.7 - Não Ficção Ligada para a Question 3</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.8 - Paper 1, Question 3: Artigo ou Discurso</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 2.9 - Paper 1, Question 3: Relatório ou Email</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Unit 2 · Writing</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 3 - Paper 2, Secção a: Discursivo e Argumentativo</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Subunit</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Production different styles: Narrative, Descriptive, Argumentative, Discursive, Letter, Summary, Report, Email, Speech - 2nd Term</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 3.1 - Escrita Discursiva - Cidades sem Carros</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Subunit</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Production different styles: Narrative, Descriptive, Argumentative, Discursive, Letter, Summary, Report, Email, Speech -1st Term</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 3.2 - Escrita Argumentativa - O Voto aos 16 Anos</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 4 - Paper 2, Secção B: Descritivo e Narrativo</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Subunit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Production different styles: Narrative, Descriptive, Argumentative, Discursive, Letter, Summary, Report, Email, Speech - 3rd Term</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 4.1 - Escrita Descritiva - Uma Estação às Sete da Manhã</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Unidade 4.2 - Escrita Narrativa - O Prédio Antes da Demolição</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Unit 3 · Speaking &amp; Listening</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Group discussion and debate - 1st Term</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Group discussion and debate - 2nd Term</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Group discussion and debate - 3rd Term</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Practice oral expression and listening comprehension - 1st Term</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Practice oral expression and listening comprehension - 2nd Term</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Practice oral expression and listening comprehension - 3rd Term</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 5 - Revisões Anuais</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Unit 4 · Grammar</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Vocabulary and grammar exercises - 1st Term</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Vocabulary and grammar exercises - 2nd Term</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Subunit</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Vocabulary and grammar exercises - 3rd Term</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 6 - Avaliação</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Unidade 7 - Atividades Extra</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D1A65A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>section_ids/name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>section_ids/chapter_ids/name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 0 - Avaliação Diagnóstica</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Diagnóstico no formato 0504: Question 1 curta de sentido explícito e implícito; parágrafo de escrita dirigida com palavras próprias, sem tópicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 1 - Paper 1, Question 1: Ficção do Século XXI</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: defender uma inferência com uma citação curta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="10" t="inlineStr"/>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: conto integral, cerca de 900 palavras, de Mário de Carvalho, Contos da Sétima Esfera</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: sentido explícito e atitude implícita do narrador (R1, R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="10" t="inlineStr"/>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: respostas curtas em frases completas, com palavras próprias e sem tópicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="10" t="inlineStr"/>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: citação integrada na frase; concordância de género e número (W5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2 - Ficção e Não Ficção dos Séculos XX e XXI</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.1 - Paper 1, Question 2: Imagem e Estrutura</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: explicar um efeito, nomeando a palavra e o efeito no leitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="10" t="inlineStr"/>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: excerto descritivo, a cidade depois da chuva, com imagem sensorial, metáfora e comparação</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="10" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: como a linguagem e a estrutura influenciam o leitor (R4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="10" t="inlineStr"/>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: parágrafo de análise, não um resumo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: conotação; variedade de inícios de frase (W3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.2 - Paper 1, Question 2: Voz, Ironia e Enviesamento</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: distinguir facto, opinião e enviesamento num artigo lido em voz alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: artigo de revista do século XXI que parece neutro</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr"/>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: atitude do autor e seleção da informação (R2, R3, R4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: comentário ao ponto de vista, só com suporte do texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: modalização (parece, talvez, é certo que); registo (W4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.3 - Texto Narrativo - Maria Judite de Carvalho - As Palavras Poupadas</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: ler uma passagem e dizer o que fica por dizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="10" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: um conto integral da coletânea</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: implícito, silêncio e ponto de vista (R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10" t="inlineStr"/>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: resposta desenvolvida com duas citações explicadas (R3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="10" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: frase complexa; pontuação da citação (W5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.4 - Literaturas de Língua Portuguesa dos Séculos XX e XXI</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.5 - Texto Narrativo - José Saramago - A Viagem do Elefante</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: apresentar um episódio e o efeito da ironia, com um plano breve</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="10" t="inlineStr"/>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: leitura integral em partes. Obra longa do ano, século XXI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="10" t="inlineStr"/>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: poder, viagem e tom irónico; efeitos de linguagem (R4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="10" t="inlineStr"/>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: análise de um excerto, com vocabulário próprio</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="10" t="inlineStr"/>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: discurso indireto; variedade de estruturas frásicas (W3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.6 - Texto Narrativo - Mia Couto - O Embondeiro que Sonhava Pássaros</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: explicar duas imagens e o que sugerem</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="10" t="inlineStr"/>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: conto integral, de Cada homem é uma raça</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="10" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: imagem, símbolo e atitude perante o lugar e as pessoas (R4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="10" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: parágrafo sobre o efeito de uma imagem, com suporte do texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="10" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: recursos figurativos (metáfora, comparação, personificação) ao serviço do efeito</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.7 - Não Ficção Ligada para a Question 3</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.8 - Paper 1, Question 3: Artigo ou Discurso</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: discurso de dois minutos só com ideias dos dois textos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="10" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: dois textos não ficcionais ligados, sobre desporto de competição na adolescência</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="10" t="inlineStr"/>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: selecionar, comparar e avaliar ideias dos dois textos, sem ideias de fora (R3, R5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="10" t="inlineStr"/>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: artigo ou discurso, 300 a 350 palavras, com introdução, desenvolvimento e conclusão</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="10" t="inlineStr"/>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: conectores de contraste e de causa; registo público (W2, W4, W5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 2.9 - Paper 1, Question 3: Relatório ou Email</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Oralidade: apresentar as recomendações de um relatório</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="10" t="inlineStr"/>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Leitura: dois textos não ficcionais ligados, sobre a praça de um bairro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="10" t="inlineStr"/>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: usar os dois textos e não acrescentar factos exteriores</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="10" t="inlineStr"/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: relatório ou email, 250 a 350 palavras</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="10" t="inlineStr"/>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: registo formal; pontuação própria do email e do relatório (W4, W5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 3 - Paper 2, Secção a: Discursivo e Argumentativo</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Leitura: um ensaio e um blogue do século XXI sobre trabalhar enquanto se estuda</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="10" t="inlineStr"/>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: distinguir exame equilibrado dos dois lados e defesa de uma tese</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="10" t="inlineStr"/>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: uma resposta discursiva e uma resposta argumentativa, 350 a 450 palavras</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="10" t="inlineStr"/>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: frase complexa; ortografia, acentuação e parágrafos (W3, W5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 3.1 - Escrita Discursiva - Cidades sem Carros</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Leitura: dois artigos com posições diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="10" t="inlineStr"/>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: cada lado com factos, ideias e objeções</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="10" t="inlineStr"/>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: texto discursivo, 350 a 450 palavras, com os dois lados e uma conclusão</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="10" t="inlineStr"/>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: conectores de equilíbrio (por um lado, por outro, contudo); W2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 3.2 - Escrita Argumentativa - O Voto aos 16 Anos</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Leitura: um artigo de opinião e um comentário de leitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="10" t="inlineStr"/>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: tese, argumentos e resposta à objeção</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="10" t="inlineStr"/>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: texto argumentativo, 350 a 450 palavras, uma posição clara</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="10" t="inlineStr"/>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: modalização e verbos de posição; precisão vocabular (W3, W4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 4 - Paper 2, Secção B: Descritivo e Narrativo</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 4.1 - Escrita Descritiva - Uma Estação às Sete da Manhã</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Leitura: um excerto descritivo do século XX ou XXI, como modelo de efeitos</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="10" t="inlineStr"/>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: o que a descrição faz o leitor ver, ouvir e sentir (R4, W1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="10" t="inlineStr"/>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: texto descritivo, 350 a 450 palavras, sem transformar a descrição numa história</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="10" t="inlineStr"/>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: vocabulário sensorial; frases longas e curtas de propósito (W3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 4.2 - Escrita Narrativa - O Prédio Antes da Demolição</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Leitura: um conto curto com viragem, como modelo de sequência</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="10" t="inlineStr"/>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Educação literária: sequência de acontecimentos, viragem e fecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="10" t="inlineStr"/>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Escrita: narrativa, 350 a 450 palavras, real ou imaginada</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="10" t="inlineStr"/>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Gramática: tempos verbais coerentes; pontuação do diálogo (W5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="51" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 5 - Revisões Anuais</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Revisões 0504: um Paper 1 completo (conto, efeitos da linguagem, escrita dirigida) e um Paper 2 (uma escolha da Secção A e uma da Secção B). Provas anteriores a 2025 tinham resumo; de 2025 a 2027 a Question 3 é escrita dirigida</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 6 - Avaliação</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Past papers 0504, condições de exame: Paper 1, 2 horas, três textos, sem dicionário; Paper 2, 2 horas, 350 a 450 palavras. Plano, palavras próprias, sem tópicos, releitura final</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Unidade 7 - Atividades Extra</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Arquivo semanal de géneros do século XX e XXI: conto, excerto de prosa, excerto de teatro, blogue, ensaio, crítica e artigo, treinados no formato das past papers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>